--- a/results/job_matches_2026-06-16.xlsx
+++ b/results/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Athena, S3, RDS, Azure, GCP, Hadoop, Hive, HBase, Flume</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b0a40d5ab0154f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c843452e183915</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Hive</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af67504e645c60dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b8b0a40d5ab0154f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a12a261b9e6a632</t>
+          <t>https://www.indeed.com/viewjob?jk=af67504e645c60dd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=1a12a261b9e6a632</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Big Data Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
+          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Delivery Engineer - Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6519ef075cdcd8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Big Data Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
+          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data/AI Engineer</t>
+          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Delivery Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
+          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data/AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
+          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
+          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
+          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
+          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Senior Developer - Research and Development</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfed31703370bf21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc40f95617fae929</t>
+          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer – GCP</t>
+          <t>Data Engineer (Databricks / Spark)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>savantys solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a567e58b2e46721</t>
+          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ingeniero SR de Herramientas de Datos</t>
+          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Millicom</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mora, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
+          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617f19a79feb89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc40f95617fae929</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineering Specialist</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
+          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Data Engineer – GCP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a567e58b2e46721</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React)</t>
+          <t>Ingeniero SR de Herramientas de Datos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Millicom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Mora, LA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
+          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise AI Products</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
+          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
+          <t>Software Engineering Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
+          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Lazer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Techster IT Services</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI / ML Platform Engineer</t>
+          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,102 +1826,102 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
+          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc9c15fd9f327ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WPP</t>
+          <t>Techster IT Services</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Tool / Platform Engineer</t>
+          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
+          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT - Developer II - IV (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Cincinnati Insurance Companies</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
+          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=027585aac274810e</t>
+          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Operational Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI / ML Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
+          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
+          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Manufacturing Data Architect</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hyosung</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e3aebf070d07cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (LEAPS)</t>
+          <t>Data Management Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b11dc54127b1ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BMG360</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd68b0031f7b250</t>
+          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc9c15fd9f327ad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (Full-Stack / Backend / Frontend)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>REVIVE SOFTWARE SYSTEMS INC</t>
+          <t>WPP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde5a67a5251cda6</t>
+          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II, Cloud Engineering</t>
+          <t>Senior Tool / Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
+          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>IT - Developer II - IV (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Cincinnati Insurance Companies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Operational Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Texas General Land Office</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
+          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,137 +2631,137 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
+          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Microservices &amp; Event-Driven Platforms)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, MongoDB, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7618d6a6e8a161c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-MFG</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,40 +2771,845 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
+          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python / AWS)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QA Automation - Plano, TX</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Photon</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d328429d08cb4a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Manufacturing Data Architect</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hyosung</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2c2d36d7fdf653b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Manufacturing Data Architect</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hyosung</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36e3aebf070d07cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Public Sector (LEAPS)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b11dc54127b1ef5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Aritzia</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Coloplast</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Global Partners LP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Cloud Engineering</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Axon</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Engineer - Azure, Databricks</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Texas Comptroller of Public Accounts</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Texas General Land Office</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Fidelity Investments</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Azure Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Engineer - Azure, Databricks</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Rochester Regional Health</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ef994aa063803e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Association of Universities for Research in Astronomy</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Atlas Travel &amp; Technology Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1d1a20831f41bca</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Microservices &amp; Event-Driven Platforms)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, MongoDB, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7618d6a6e8a161c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-MFG</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Senior Software Engineer, Data Governance &amp; Foundations</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Instacart</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D91" t="n">
         <v>10.4</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Databricks, Spark, Scala, Kafka, Snowflake, ELT, dbt, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=50dcbfff992c7b48</t>
         </is>

--- a/results/job_matches_2026-06-16.xlsx
+++ b/results/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a12a261b9e6a632</t>
+          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IKS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,242 +636,242 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=1a12a261b9e6a632</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6519ef075cdcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Big Data Developer</t>
+          <t>Co-Founder &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
+          <t>https://www.indeed.com/viewjob?jk=b3136af621d112cd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
+          <t>Databricks Solution Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Delivery Engineer - Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6519ef075cdcd8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Ideas2IT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
+          <t>https://www.indeed.com/viewjob?jk=58202b65be5a1bb5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data/AI Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e6748d22408c01a3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Senior Big Data Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
+          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Delivery Engineer - Data</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
+          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
+          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data/AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
+          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
+          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Developer - Research and Development</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfed31703370bf21</t>
+          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,49 +1196,49 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
+          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks / Spark)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>savantys solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Senior Developer - Research and Development</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfed31703370bf21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Databricks / Spark)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>savantys solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc40f95617fae929</t>
+          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
+          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer – GCP</t>
+          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a567e58b2e46721</t>
+          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
+          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ingeniero SR de Herramientas de Datos</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Millicom</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mora, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Spark, Scala, PostgreSQL, MongoDB, DynamoDB, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de52afff18be3da</t>
+          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Dynatrace</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, clustering keys, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e40e1e6f5dca3a9f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Specialist</t>
+          <t>Data Engineer – GCP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
+          <t>https://www.indeed.com/viewjob?jk=6a567e58b2e46721</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lazer</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineering Specialist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
+          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Lazer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
+          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise AI Products</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
+          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Techster IT Services</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
+          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
+          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Techster IT Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI / ML Platform Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
+          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
+          <t>AI / ML Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
+          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
+          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Management Specialist</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
+          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BMG360</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Management Specialist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc9c15fd9f327ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WPP</t>
+          <t>BMG360</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Tool / Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc9c15fd9f327ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT - Developer II - IV (Remote)</t>
+          <t>Digital Site Reliability Sr Engg.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Cincinnati Insurance Companies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
+          <t>https://www.indeed.com/viewjob?jk=43a12edd3543ad18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Operational Engineer II</t>
+          <t>Senior Tool / Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
+          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT - Developer II - IV (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>The Cincinnati Insurance Companies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Jaggaer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Operational Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
+          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f1fbccd2f80abc</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (LEAPS)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,112 +2971,112 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b11dc54127b1ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Coloplast</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II, Cloud Engineering</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Aritzia</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
+          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Texas General Land Office</t>
+          <t>Coloplast</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
+          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
+          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Software Engineer II, Cloud Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
+          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+          <t>Data Engineer - Azure, Databricks</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Texas General Land Office</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ef994aa063803e</t>
+          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Association of Universities for Research in Astronomy</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
+          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Atlas Travel &amp; Technology Group, Inc.</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d1a20831f41bca</t>
+          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Microservices &amp; Event-Driven Platforms)</t>
+          <t>Data Engineer - Azure, Databricks</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, MongoDB, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7618d6a6e8a161c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist-MFG</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
+          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Governance &amp; Foundations</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, ELT, dbt, Airflow, Apache Airflow, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,147 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50dcbfff992c7b48</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ef994aa063803e</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Association of Universities for Research in Astronomy</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Association of Universities for Research in Astronomy</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HI, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009b9d64b783c574</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Microservices &amp; Event-Driven Platforms)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, MongoDB, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7618d6a6e8a161c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist-MFG</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-16.xlsx
+++ b/results/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,52 +783,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ideas2IT</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, RDS, Azure, GCP, Dataflow, Vertex AI, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58202b65be5a1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=e6748d22408c01a3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Applications Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>AAA The Auto Club Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6748d22408c01a3</t>
+          <t>https://www.indeed.com/viewjob?jk=904c19f690af9670</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Big Data Developer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
+          <t>https://www.indeed.com/viewjob?jk=791f6ef1e634abe3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
+          <t>Delivery Engineer - Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Delivery Engineer - Data</t>
+          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
+          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data/AI Engineer</t>
+          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
+          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Data/AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data and Analytics Engineer (Hybrid)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Velir</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid</t>
+          <t>Senior Developer - Research and Development</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tarrytown, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
+          <t>https://www.indeed.com/viewjob?jk=dfed31703370bf21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Developer - Research and Development</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfed31703370bf21</t>
+          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer (Databricks / Spark)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>savantys solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks / Spark)</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>savantys solutions</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
+          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dynatrace</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, clustering keys, ETL, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e40e1e6f5dca3a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer – GCP</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Signifyd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a567e58b2e46721</t>
+          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Dynatrace</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, clustering keys, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e40e1e6f5dca3a9f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering Specialist</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lazer</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineering Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Looker &amp; Quicksight Admin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Stradit</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, Kimball, ETL, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
+          <t>https://www.indeed.com/viewjob?jk=50b38fe2a532eb0d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Looker &amp; Quicksight Admin</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Stradit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, Kimball, ETL, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
+          <t>https://www.indeed.com/viewjob?jk=14fc862e5d3c6940</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React)</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Lazer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
+          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Techster IT Services</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Unity Catalog, Scala, Databricks Lakehouse, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
+          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
+          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI / ML Platform Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Data Management Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Management Specialist</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>BMG360</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
+          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Digital Site Reliability Sr Engg.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BMG360</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=43a12edd3543ad18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>IT - Developer II - IV (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Cincinnati Insurance Companies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc9c15fd9f327ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Digital Site Reliability Sr Engg.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43a12edd3543ad18</t>
+          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Tool / Platform Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
+          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT - Developer II - IV (Remote)</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Cincinnati Insurance Companies</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f1fbccd2f80abc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>QA Automation - Plano, TX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+          <t>https://www.indeed.com/viewjob?jk=3d328429d08cb4a5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Manufacturing Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Hyosung</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c2d36d7fdf653b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f1fbccd2f80abc</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QA Automation - Plano, TX</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d328429d08cb4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Manufacturing Data Architect</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hyosung</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c2d36d7fdf653b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Manufacturing Data Architect</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hyosung</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,172 +2946,172 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e3aebf070d07cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Rochester Regional Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ef994aa063803e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
+          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
+          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Cloud Engineer (AWS)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Otoe Missouria Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Aritzia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Coloplast</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f878ef67cdc8cf7</t>
+          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
+          <t>Software Engineer II, Cloud Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Azure, Databricks</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Coloplast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II, Cloud Engineering</t>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Texas General Land Office</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
+          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
+          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
+          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Senior Software Engineer (Backend) | .Net | Onsite | Local to Tennessee | Onsite | 10 years exp.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Texas General Land Office</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mount Juliet, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
+          <t>https://www.indeed.com/viewjob?jk=40aed3ab499de0ef</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Association of Universities for Research in Astronomy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
+          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Association of Universities for Research in Astronomy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
+          <t>https://www.indeed.com/viewjob?jk=009b9d64b783c574</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
+          <t>Lakebase Sales Specialist-MFG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3505,251 +3505,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineer - Azure, Databricks</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>DailyPay Inc</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Rochester Regional Health</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ef994aa063803e</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Association of Universities for Research in Astronomy</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Association of Universities for Research in Astronomy</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=009b9d64b783c574</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Solutions Architect (Microservices &amp; Event-Driven Platforms)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, MongoDB, CI/CD, GitHub Actions, Maven, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7618d6a6e8a161c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist-MFG</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
         </is>

--- a/results/job_matches_2026-06-16.xlsx
+++ b/results/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,35 +783,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6748d22408c01a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Delivery Engineer - Data</t>
+          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ollion</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
+          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
+          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POOLCORP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Covington, LA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Dimensional Modeling, Kimball, Star Schema</t>
+          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
+          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Data Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
+          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data/AI Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid</t>
+          <t>Senior Cassandra Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8c2058057ef3c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>American Institutes for Research</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,94 +1231,94 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=57ff148546ca71ca</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Developer - Research and Development</t>
+          <t>Data Engineer (Databricks / Spark)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>savantys solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tarrytown, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Data Modeling, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfed31703370bf21</t>
+          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
+          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (Databricks / Spark)</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>savantys solutions</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,137 +1336,137 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a88bae140fdb8d9</t>
+          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, dbt, MLOps</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
+          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Signifyd</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, ECS, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineering Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,77 +1536,77 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
+          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dynatrace</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, clustering keys, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e40e1e6f5dca3a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aeea00b4604b283</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Lazer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering Specialist</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
+          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Looker &amp; Quicksight Admin</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stradit</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, Kimball, ETL, Amazon QuickSight, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b38fe2a532eb0d</t>
+          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Looker &amp; Quicksight Admin</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stradit</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, Kimball, ETL, Amazon QuickSight, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fc862e5d3c6940</t>
+          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
+          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lazer</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, GCP, Cloud Storage, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,94 +1931,94 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, MySQL, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77837a031fc53f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Software Delivery Analyst - Social, Healthcare and Public Entities</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, RDS, Databricks, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
+          <t>https://www.indeed.com/viewjob?jk=48b95397ee215eb4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BMG360</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
+          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
+          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Jaggaer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Operational Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,54 +2176,54 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4182e14591bf9062</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,151 +2232,151 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Management Specialist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BMG360</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Digital Site Reliability Sr Engg.</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43a12edd3543ad18</t>
+          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT - Developer II - IV (Remote)</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Cincinnati Insurance Companies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8fa791c147f481</t>
+          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,77 +2446,77 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Spark, PySpark, Scala, ETL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27c4c94d4bb1096</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Miami</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3acf52fb0bcdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
+          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Cloud Engineer (AWS)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jaggaer</t>
+          <t>Otoe Missouria Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Operational Engineer II</t>
+          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>Aritzia</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
+          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Coloplast</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer II, Cloud Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f1fbccd2f80abc</t>
+          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QA Automation - Plano, TX</t>
+          <t>Data Engineer - Azure, Databricks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d328429d08cb4a5</t>
+          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Manufacturing Data Architect</t>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hyosung</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,199 +2771,199 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c2d36d7fdf653b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>GLO - Senior Data Engineer (Programmer V)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Texas General Land Office</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
+          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
+          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
+          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Software Architect (Java, AWS, &amp; AI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b35823372d99142</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rochester Regional Health</t>
+          <t>Association of Universities for Research in Astronomy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Data Modeling, ETL, Power BI</t>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ef994aa063803e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Association of Universities for Research in Astronomy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,497 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location OPEN</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f330adaec1c495e</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Cloud Engineer (AWS)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Otoe Missouria Group</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Aritzia</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Coloplast</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Cloud Engineering</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Axon</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer - Azure, Databricks</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Texas Comptroller of Public Accounts</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Texas General Land Office</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Fidelity Investments</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Azure Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Nebius</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Backend) | .Net | Onsite | Local to Tennessee | Onsite | 10 years exp.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Tms Llc</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Mount Juliet, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40aed3ab499de0ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Association of Universities for Research in Astronomy</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Association of Universities for Research in Astronomy</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=009b9d64b783c574</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist-MFG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a58245b44978dc16</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-16.xlsx
+++ b/results/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8b0a40d5ab0154f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb438bd3c8e9afd7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af67504e645c60dd</t>
+          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
+          <t>Ruby on Rails Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Program Management Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, RDS, Azure, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,49 +601,49 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
+          <t>https://www.indeed.com/viewjob?jk=51965b97284dee62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Co-Founder &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a12a261b9e6a632</t>
+          <t>https://www.indeed.com/viewjob?jk=b3136af621d112cd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,46 +657,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
+          <t>https://www.indeed.com/viewjob?jk=a06c99225161e1ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Database Engineer</t>
+          <t>Databricks Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3136af621d112cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6c6519ef075cdcd8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optimus Health Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6519ef075cdcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
         </is>
       </c>
     </row>
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Spark, PySpark, Scala, Snowflake, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97655a66d7c65a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (AI/ML)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer - Hybrid</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visibol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=82b0ee3ccd5cda5d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cassandra Database Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>RDS, Hadoop, HDFS, Hive, Oozie, YARN, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c8c2058057ef3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e78837301757164c</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Mike Albert Leasing, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, Data Modeling, ETL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b10fbdd189c8206</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Junior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Mojo Family of Brands</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alcoa, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
+          <t>https://www.indeed.com/viewjob?jk=1b317dade1a4e740</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
+          <t>https://www.indeed.com/viewjob?jk=d27cedf4e30a5878</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
+          <t>https://www.indeed.com/viewjob?jk=81630a7975019375</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Signifyd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, Cassandra, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>AKUNA CAPITAL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa6c5af5f79093d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6681b1e5ed6ead</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
+          <t>MuleSoft Consultant</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>RADIX INTERNATIONAL CONSULTING</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,28 +1777,28 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
+          <t>https://www.indeed.com/viewjob?jk=151dfd13a3d3fb99</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
+          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
+          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Scala, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
+          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2017737c2d0bf38</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Magpie Health Analytics</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Delivery Analyst - Social, Healthcare and Public Entities</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Magpie Health Analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Splunk, MicroStrategy, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b95397ee215eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1aa5ffe62a0a2d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMG360</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
+          <t>Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
+          <t>https://www.indeed.com/viewjob?jk=46bb1265645f6218</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>BMG360</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, GCP, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
+          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jaggaer</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Oracle, SQL Server, ETL, Tableau, MS Excel, MicroStrategy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
+          <t>https://www.indeed.com/viewjob?jk=1df8e9d2986ffdcc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Operational Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CSG</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Hadoop, Spark, Scala, ETL, MLOps, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
+          <t>https://www.indeed.com/viewjob?jk=af85563e825137c3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
+          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Jaggaer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
+          <t>https://www.indeed.com/viewjob?jk=b7169dd4a9327364</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Operational Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>CSG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, ETL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6cb5b5519b1508</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, MapReduce, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f968a50a71646</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3009a7e9a55c62</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Spark, PySpark, Scala, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8b21c3d1ca0b67</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, Azure, GCP, HBase, Scala, Kafka, Oracle, PostgreSQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer - FDE (Fullstack) - Digital Native Business</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wexford, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2bd7502c607488</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Engineer (AWS)</t>
+          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Otoe Missouria Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Spark, PySpark, Scala, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b33dd94cf4d6d3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Coloplast</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
+          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II, Cloud Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5535a7227c62c60b</t>
+          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>Cloud Engineer (AWS)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Otoe Missouria Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2bbecc8dae238d3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Aritzia</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3e9f76b8e11395</t>
+          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GLO - Senior Data Engineer (Programmer V)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Texas General Land Office</t>
+          <t>Coloplast</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aead3a13f39a33da</t>
+          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Architect (Java, AWS, &amp; AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e56d3a3b1f5f32</t>
+          <t>https://www.indeed.com/viewjob?jk=8b35823372d99142</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Azure DevOps Engineer &amp; Administrator</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nebius</t>
+          <t>Tra'Bian Enterprises</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, PostgreSQL, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
+          <t>https://www.indeed.com/viewjob?jk=658850a071f96269</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Architect (Java, AWS, &amp; AI)</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b35823372d99142</t>
+          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Association of Universities for Research in Astronomy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, Data Modeling, ETL, Git, Python, SQL</t>
+          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1d1d8b402f1a5e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
         </is>
       </c>
     </row>
@@ -2976,45 +2976,10 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea84ae0bf135a727</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Association of Universities for Research in Astronomy</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>HI, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, PostgreSQL, ELT, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=009b9d64b783c574</t>
         </is>
